--- a/数据集.xlsx
+++ b/数据集.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13211" windowHeight="9335"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1575,7 +1575,7 @@
         <v>1.14</v>
       </c>
       <c r="F11">
-        <v>2.21</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1617,7 +1617,7 @@
         <v>2.34</v>
       </c>
       <c r="F12">
-        <v>2.21</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>1</v>
